--- a/TrackGestora.xlsx
+++ b/TrackGestora.xlsx
@@ -8,31 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlo Taranto\Progetti_Tech\Personali\Gestora\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857250CB-F6C2-4318-8CA5-9BFC29E85A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542B8B93-33EF-44B2-8326-7505B801CB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="30960" windowHeight="12120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
-    <sheet name="BE · Models" sheetId="2" r:id="rId2"/>
-    <sheet name="BE · DTO" sheetId="3" r:id="rId3"/>
-    <sheet name="BE · Repository" sheetId="4" r:id="rId4"/>
-    <sheet name="BE · Services" sheetId="5" r:id="rId5"/>
-    <sheet name="BE · Controllers" sheetId="6" r:id="rId6"/>
-    <sheet name="BE · Method" sheetId="7" r:id="rId7"/>
-    <sheet name="BE · Validators" sheetId="8" r:id="rId8"/>
-    <sheet name="BE · Infrastruttura" sheetId="9" r:id="rId9"/>
-    <sheet name="BE · Test" sheetId="10" r:id="rId10"/>
-    <sheet name="BE · Auth e Security" sheetId="11" r:id="rId11"/>
-    <sheet name="BE · Jobs" sheetId="12" r:id="rId12"/>
-    <sheet name="BE · Migration" sheetId="13" r:id="rId13"/>
-    <sheet name="FE · Pagine" sheetId="14" r:id="rId14"/>
-    <sheet name="FE · Componenti" sheetId="15" r:id="rId15"/>
-    <sheet name="FE · Hook e API" sheetId="16" r:id="rId16"/>
-    <sheet name="FE · Auth" sheetId="17" r:id="rId17"/>
-    <sheet name="FE · Test" sheetId="18" r:id="rId18"/>
-    <sheet name="Appunti e Step" sheetId="19" r:id="rId19"/>
-    <sheet name="Fix e Bug" sheetId="20" r:id="rId20"/>
+    <sheet name="Appunti e Step" sheetId="19" r:id="rId2"/>
+    <sheet name="Fix e Bug" sheetId="20" r:id="rId3"/>
+    <sheet name="BE · Models" sheetId="2" r:id="rId4"/>
+    <sheet name="BE · DTO" sheetId="3" r:id="rId5"/>
+    <sheet name="BE · Repository" sheetId="4" r:id="rId6"/>
+    <sheet name="BE · Services" sheetId="5" r:id="rId7"/>
+    <sheet name="BE · Controllers" sheetId="6" r:id="rId8"/>
+    <sheet name="BE · Method" sheetId="7" r:id="rId9"/>
+    <sheet name="BE · Validators" sheetId="8" r:id="rId10"/>
+    <sheet name="BE · Infrastruttura" sheetId="9" r:id="rId11"/>
+    <sheet name="BE · Test" sheetId="10" r:id="rId12"/>
+    <sheet name="BE · Auth e Security" sheetId="11" r:id="rId13"/>
+    <sheet name="BE · Jobs" sheetId="12" r:id="rId14"/>
+    <sheet name="BE · Migration" sheetId="13" r:id="rId15"/>
+    <sheet name="FE · Pagine" sheetId="14" r:id="rId16"/>
+    <sheet name="FE · Componenti" sheetId="15" r:id="rId17"/>
+    <sheet name="FE · Hook e API" sheetId="16" r:id="rId18"/>
+    <sheet name="FE · Auth" sheetId="17" r:id="rId19"/>
+    <sheet name="FE · Test" sheetId="18" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="1346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="1364">
   <si>
     <t>GESTORA — CRUSCOTTO DEL PROGETTO</t>
   </si>
@@ -2457,15 +2457,9 @@
     <t>PrenotazioneCreateDTOValidator</t>
   </si>
   <si>
-    <t>Coperti da 1 a 50, data fra oggi e un anno, fascia valida, note max 500</t>
-  </si>
-  <si>
     <t>CheckDisponibilitaDTOValidator</t>
   </si>
   <si>
-    <t>Coperti da 1 a 50, data fra oggi e un anno</t>
-  </si>
-  <si>
     <t>RegisterDTOValidator</t>
   </si>
   <si>
@@ -4044,9 +4038,6 @@
     <t>Il tetto di 50 coperti per prenotazione è fisso nel codice</t>
   </si>
   <si>
-    <t>Renderlo configurabile: A) valore in appsettings (consigliata) o B) impostazione dell'Admin nel database</t>
-  </si>
-  <si>
     <t>Fatto</t>
   </si>
   <si>
@@ -4071,9 +4062,6 @@
     <t>Strutturata come linea guida da cui prendere esempio per la messa in piedi di altri progetti (DA FARE A PROGETTO CHIUSO)</t>
   </si>
   <si>
-    <t>Aggiornato il 05/10/2026 · Gestora v2 in corso · BE e FE sono in fogli separati (prefisso BE · e FE ·)</t>
-  </si>
-  <si>
     <t>Storico delle versioni precedenti</t>
   </si>
   <si>
@@ -4090,6 +4078,72 @@
   </si>
   <si>
     <t>V2-003</t>
+  </si>
+  <si>
+    <t>V2-006</t>
+  </si>
+  <si>
+    <t>gestire il tetto di 100 coperti e renderlo raggiungibile</t>
+  </si>
+  <si>
+    <t>Aggiornato il 06/10/2026 · Gestora v2 in corso · BE e FE sono in fogli separati (prefisso BE · e FE ·)</t>
+  </si>
+  <si>
+    <t>Fatto: tetto in configurazione (Prenotazioni:MaxCopertiPerPrenotazione, 50), letto dai validatori; pagina pubblica lo legge da GET limiti-prenotazione e oltre il tetto invita a contattare il ristorante</t>
+  </si>
+  <si>
+    <t>V2-007</t>
+  </si>
+  <si>
+    <t>FE</t>
+  </si>
+  <si>
+    <t>Pagina pubblica: components/landing/VerificaDisponibilita.tsx</t>
+  </si>
+  <si>
+    <t>Fascia non prenotabile mostra sempre «Disponibilità residua: N» + «Pieno», anche se il motivo sono i tavoli o la fascia già finita</t>
+  </si>
+  <si>
+    <t>Analizzato, correzione rimandata: soluzioni in BACKLOG.md</t>
+  </si>
+  <si>
+    <t>/api/Prenotazione/limiti-prenotazione</t>
+  </si>
+  <si>
+    <t>GetLimitiPrenotazione</t>
+  </si>
+  <si>
+    <t>Tetto dei coperti per prenotazione, dalla configurazione</t>
+  </si>
+  <si>
+    <t>LimitiPrenotazioneDTO</t>
+  </si>
+  <si>
+    <t>Limiti che il frontend usa nei form</t>
+  </si>
+  <si>
+    <t>MaxCopertiPerPrenotazione</t>
+  </si>
+  <si>
+    <t>Coperti da 1 al tetto in configurazione (oggi 50), data fra oggi e un anno, fascia valida, note max 500</t>
+  </si>
+  <si>
+    <t>Coperti da 1 al tetto in configurazione (oggi 50), data fra oggi e un anno</t>
+  </si>
+  <si>
+    <t>PrenotazioniSettings</t>
+  </si>
+  <si>
+    <t>Tetto dei coperti per prenotazione (Prenotazioni:MaxCopertiPerPrenotazione), controllato all'avvio: deve essere &gt; 0</t>
+  </si>
+  <si>
+    <t>useLimitiPrenotazione</t>
+  </si>
+  <si>
+    <t>Prenotazione/limiti-prenotazione</t>
+  </si>
+  <si>
+    <t>Tetto dei coperti (anche senza login)</t>
   </si>
 </sst>
 </file>
@@ -4379,6 +4433,10 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -4387,158 +4445,11 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="60">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF595959"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF595959"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -5176,6 +5087,149 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF595959"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF595959"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -5325,7 +5379,7 @@
                   <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>32</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>43</c:v>
@@ -5334,7 +5388,7 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>65</c:v>
@@ -5343,7 +5397,7 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>30</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>22</c:v>
@@ -5364,7 +5418,7 @@
                   <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>39</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>13</c:v>
@@ -5376,7 +5430,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5510,6 +5564,32 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="BE_DTO" displayName="BE_DTO" ref="A4:D37">
+  <autoFilter ref="A4:D37" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="DTO"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Area"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Serve a"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Campi principali"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="BE_Repository" displayName="BE_Repository" ref="A4:D47">
+  <autoFilter ref="A4:D47" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Repository"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Metodo"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Cosa fa"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Note"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="BE_Services" displayName="BE_Services" ref="A4:F20">
   <autoFilter ref="A4:F20" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="6">
@@ -5524,9 +5604,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="BE_Controllers" displayName="BE_Controllers" ref="A4:G58">
-  <autoFilter ref="A4:G58" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="BE_Controllers" displayName="BE_Controllers" ref="A4:G59">
+  <autoFilter ref="A4:G59" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="Controller"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Verbo"/>
@@ -5540,7 +5620,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="BE_Method" displayName="BE_Method" ref="A4:E69">
   <autoFilter ref="A4:E69" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
   <tableColumns count="5">
@@ -5554,7 +5634,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="BE_Validators" displayName="BE_Validators" ref="A4:C13">
   <autoFilter ref="A4:C13" xr:uid="{00000000-0009-0000-0100-00000D000000}"/>
   <tableColumns count="3">
@@ -5566,9 +5646,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="BE_Infrastruttura" displayName="BE_Infrastruttura" ref="A4:C34">
-  <autoFilter ref="A4:C34" xr:uid="{00000000-0009-0000-0100-00000E000000}"/>
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="BE_Infrastruttura" displayName="BE_Infrastruttura" ref="A4:C35">
+  <autoFilter ref="A4:C35" xr:uid="{00000000-0009-0000-0100-00000E000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="Componente"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="Tipo"/>
@@ -5578,7 +5658,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF0E000000}" name="BE_Test" displayName="BE_Test" ref="A4:E26">
   <autoFilter ref="A4:E26" xr:uid="{00000000-0009-0000-0100-00000F000000}"/>
   <tableColumns count="5">
@@ -5592,7 +5672,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF0F000000}" name="BE_Auth_e_Security" displayName="BE_Auth_e_Security" ref="A4:C29">
   <autoFilter ref="A4:C29" xr:uid="{00000000-0009-0000-0100-000010000000}"/>
   <tableColumns count="3">
@@ -5604,7 +5684,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF10000000}" name="BE_Jobs" displayName="BE_Jobs" ref="A4:F6">
   <autoFilter ref="A4:F6" xr:uid="{00000000-0009-0000-0100-000011000000}"/>
   <tableColumns count="6">
@@ -5619,7 +5699,18 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="FixPerStato" displayName="FixPerStato" ref="F35:G39">
+  <autoFilter ref="F35:G39" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="2">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Stato"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Quanti"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00000000-000C-0000-FFFF-FFFF11000000}" name="BE_Migration" displayName="BE_Migration" ref="A4:G11">
   <autoFilter ref="A4:G11" xr:uid="{00000000-0009-0000-0100-000012000000}"/>
   <tableColumns count="7">
@@ -5635,7 +5726,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{00000000-000C-0000-FFFF-FFFF12000000}" name="FE_Pagine" displayName="FE_Pagine" ref="A4:D16">
   <autoFilter ref="A4:D16" xr:uid="{00000000-0009-0000-0100-000013000000}"/>
   <tableColumns count="4">
@@ -5648,18 +5739,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="FixPerStato" displayName="FixPerStato" ref="F35:G39">
-  <autoFilter ref="F35:G39" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="2">
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Stato"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Quanti"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF13000000}" name="FE_Componenti" displayName="FE_Componenti" ref="A4:D32">
   <autoFilter ref="A4:D32" xr:uid="{00000000-0009-0000-0100-000014000000}"/>
   <tableColumns count="4">
@@ -5672,9 +5752,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{00000000-000C-0000-FFFF-FFFF14000000}" name="FE_Hook_e_API" displayName="FE_Hook_e_API" ref="A4:F43">
-  <autoFilter ref="A4:F43" xr:uid="{00000000-0009-0000-0100-000015000000}"/>
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{00000000-000C-0000-FFFF-FFFF14000000}" name="FE_Hook_e_API" displayName="FE_Hook_e_API" ref="A4:F44">
+  <autoFilter ref="A4:F44" xr:uid="{00000000-0009-0000-0100-000015000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1400-000001000000}" name="Hook"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-1400-000002000000}" name="Area"/>
@@ -5687,7 +5767,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{00000000-000C-0000-FFFF-FFFF15000000}" name="FE_Auth" displayName="FE_Auth" ref="A4:C17">
   <autoFilter ref="A4:C17" xr:uid="{00000000-0009-0000-0100-000016000000}"/>
   <tableColumns count="3">
@@ -5699,7 +5779,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{00000000-000C-0000-FFFF-FFFF16000000}" name="FE_Test" displayName="FE_Test" ref="A4:C13">
   <autoFilter ref="A4:C13" xr:uid="{00000000-0009-0000-0100-000017000000}"/>
   <tableColumns count="3">
@@ -5708,39 +5788,6 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-1600-000003000000}" name="N. test"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{00000000-000C-0000-FFFF-FFFF17000000}" name="Appunti_e_Step" displayName="Appunti_e_Step" ref="A4:F34">
-  <autoFilter ref="A4:F34" xr:uid="{00000000-0009-0000-0100-000018000000}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1700-000001000000}" name="Data"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1700-000002000000}" name="Area"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1700-000003000000}" name="Cosa si è fatto"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1700-000004000000}" name="Prossimo passo"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1700-000005000000}" name="Stato"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1700-000006000000}" name="Note"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="Fix_e_Bug" displayName="Fix_e_Bug" ref="A4:I34">
-  <autoFilter ref="A4:I34" xr:uid="{00000000-0009-0000-0100-000019000000}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1800-000001000000}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1800-000002000000}" name="Data"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1800-000003000000}" name="Area"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1800-000004000000}" name="Dove"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1800-000005000000}" name="Problema"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1800-000006000000}" name="Gravità"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1800-000007000000}" name="Soluzione"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1800-000008000000}" name="Stato"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1800-000009000000}" name="Chiuso il"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -5792,6 +5839,39 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{00000000-000C-0000-FFFF-FFFF17000000}" name="Appunti_e_Step" displayName="Appunti_e_Step" ref="A4:F34">
+  <autoFilter ref="A4:F34" xr:uid="{00000000-0009-0000-0100-000018000000}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1700-000001000000}" name="Data"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1700-000002000000}" name="Area"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1700-000003000000}" name="Cosa si è fatto"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1700-000004000000}" name="Prossimo passo"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1700-000005000000}" name="Stato"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1700-000006000000}" name="Note"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="Fix_e_Bug" displayName="Fix_e_Bug" ref="A4:I34">
+  <autoFilter ref="A4:I34" xr:uid="{00000000-0009-0000-0100-000019000000}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1800-000001000000}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1800-000002000000}" name="Data"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1800-000003000000}" name="Area"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1800-000004000000}" name="Dove"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1800-000005000000}" name="Problema"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1800-000006000000}" name="Gravità"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1800-000007000000}" name="Soluzione"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1800-000008000000}" name="Stato"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1800-000009000000}" name="Chiuso il"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="BE_Models" displayName="BE_Models" ref="A4:F48">
   <autoFilter ref="A4:F48" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="6">
@@ -5801,32 +5881,6 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Tipo"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Obbligatorio"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Note"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="BE_DTO" displayName="BE_DTO" ref="A4:D36">
-  <autoFilter ref="A4:D36" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="DTO"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Area"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Serve a"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Campi principali"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="BE_Repository" displayName="BE_Repository" ref="A4:D47">
-  <autoFilter ref="A4:D47" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Repository"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Metodo"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Cosa fa"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6150,7 +6204,7 @@
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6175,7 +6229,7 @@
     <row r="5" spans="1:9" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22">
         <f>SUM('BE · Test'!D5:D1000)</f>
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="3">
@@ -6183,8 +6237,8 @@
         <v>64</v>
       </c>
       <c r="D5" s="22">
-        <f>COUNTA('BE · Controllers'!A5:A1000)</f>
-        <v>54</v>
+        <f>COUNTA('BE · Controllers'!A5:A1001)</f>
+        <v>55</v>
       </c>
       <c r="E5" s="23"/>
       <c r="F5" s="23"/>
@@ -6243,8 +6297,8 @@
         <v>15</v>
       </c>
       <c r="D10" s="8">
-        <f>COUNTA('BE · DTO'!A5:A1000)</f>
-        <v>32</v>
+        <f>COUNTA('BE · DTO'!A5:A1001)</f>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -6288,8 +6342,8 @@
         <v>21</v>
       </c>
       <c r="D13" s="8">
-        <f>COUNTA('BE · Controllers'!A5:A1000)</f>
-        <v>54</v>
+        <f>COUNTA('BE · Controllers'!A5:A1001)</f>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -6333,8 +6387,8 @@
         <v>27</v>
       </c>
       <c r="D16" s="8">
-        <f>COUNTA('BE · Infrastruttura'!A5:A1000)</f>
-        <v>30</v>
+        <f>COUNTA('BE · Infrastruttura'!A5:A1001)</f>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.3">
@@ -6438,8 +6492,8 @@
         <v>42</v>
       </c>
       <c r="D23" s="8">
-        <f>COUNTA('FE · Hook e API'!A5:A1000)</f>
-        <v>39</v>
+        <f>COUNTA('FE · Hook e API'!A5:A1001)</f>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.3">
@@ -6499,7 +6553,7 @@
       </c>
       <c r="D27" s="8">
         <f>COUNTA('Fix e Bug'!E5:E1000)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="19.2" x14ac:dyDescent="0.45">
@@ -6603,7 +6657,7 @@
       </c>
       <c r="G36" s="8">
         <f>COUNTIF('Fix e Bug'!H5:H1000,"Risolto")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>80</v>
@@ -6626,7 +6680,7 @@
       </c>
       <c r="I37" s="8">
         <f>COUNTIFS('Fix e Bug'!F5:F1000,"Media",'Fix e Bug'!H5:H1000,"&lt;&gt;Risolto",'Fix e Bug'!H5:H1000,"&lt;&gt;Scartato",'Fix e Bug'!E5:E1000,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="19.2" x14ac:dyDescent="0.45">
@@ -6662,7 +6716,7 @@
       </c>
       <c r="G39" s="8">
         <f>COUNTIF('Fix e Bug'!H5:H1000,"Scartato")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -6947,10 +7001,10 @@
     </row>
     <row r="67" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>137</v>
@@ -6961,7 +7015,7 @@
         <v>138</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>137</v>
@@ -7016,6 +7070,572 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF2E5FAD"/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
+        <v>787</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+    </row>
+    <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>789</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>790</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>792</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>794</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>796</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>798</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>800</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>801</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>802</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>804</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>806</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>807</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C2" location="'Dashboard'!A1" display="← Torna alla Dashboard" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF2E5FAD"/>
+  </sheetPr>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
+        <v>808</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+    </row>
+    <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>810</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>811</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>812</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>814</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>817</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>819</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>821</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>823</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>825</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>784</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>828</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>830</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>831</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>833</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>831</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>831</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>837</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>831</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
+        <v>839</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>831</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>841</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>844</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>846</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>848</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>850</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>852</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>854</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>856</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>858</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
+        <v>860</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>861</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A30" s="14" t="s">
+        <v>863</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>861</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
+        <v>865</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>861</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A32" s="14" t="s">
+        <v>867</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A33" s="14" t="s">
+        <v>869</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A34" s="14" t="s">
+        <v>871</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A35" s="14" t="s">
+        <v>873</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>874</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B5:B1001">
+    <cfRule type="expression" dxfId="33" priority="1">
+      <formula>$B5="Middleware"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="2">
+      <formula>$B5="Eccezione"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="3">
+      <formula>$B5="Estensione"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="4">
+      <formula>$B5="Configurazione"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="5">
+      <formula>$B5="Riga di comando"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="6">
+      <formula>$B5="Deploy"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="C2" location="'Dashboard'!A1" display="← Torna alla Dashboard" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E5FAD"/>
@@ -7030,17 +7650,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>877</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
+      <c r="A1" s="30" t="s">
+        <v>875</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="2" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>141</v>
@@ -7048,25 +7668,25 @@
     </row>
     <row r="3" spans="1:5" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A3" s="15" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B3" s="16">
         <f>SUM(D5:D1000)</f>
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
+        <v>878</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>879</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>880</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>881</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>882</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>883</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>147</v>
@@ -7074,30 +7694,30 @@
     </row>
     <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>468</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D5" s="14">
         <v>101</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>479</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D6" s="14">
         <v>25</v>
@@ -7106,47 +7726,47 @@
     </row>
     <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>463</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D7" s="14">
         <v>16</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>489</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D8" s="14">
         <v>15</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>472</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D9" s="14">
         <v>13</v>
@@ -7155,30 +7775,30 @@
     </row>
     <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>507</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D10" s="14">
         <v>13</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>475</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D11" s="14">
         <v>12</v>
@@ -7187,13 +7807,13 @@
     </row>
     <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>458</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D12" s="14">
         <v>12</v>
@@ -7202,13 +7822,13 @@
     </row>
     <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>482</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D13" s="14">
         <v>10</v>
@@ -7217,39 +7837,39 @@
     </row>
     <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>292</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D14" s="14">
         <v>9</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>789</v>
       </c>
       <c r="D15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>800</v>
@@ -7258,16 +7878,16 @@
         <v>789</v>
       </c>
       <c r="D16" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>789</v>
@@ -7276,12 +7896,12 @@
         <v>7</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>798</v>
@@ -7293,18 +7913,18 @@
         <v>5</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>453</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D19" s="14">
         <v>8</v>
@@ -7313,13 +7933,13 @@
     </row>
     <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>784</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D20" s="14">
         <v>6</v>
@@ -7328,13 +7948,13 @@
     </row>
     <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D21" s="14">
         <v>4</v>
@@ -7343,30 +7963,30 @@
     </row>
     <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>503</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D22" s="14">
         <v>3</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>426</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
@@ -7375,13 +7995,13 @@
     </row>
     <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
+        <v>916</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>918</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>919</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>920</v>
       </c>
       <c r="D24" s="14">
         <v>3</v>
@@ -7390,13 +8010,13 @@
     </row>
     <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
@@ -7405,13 +8025,13 @@
     </row>
     <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D26" s="14">
         <v>2</v>
@@ -7423,25 +8043,25 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C1000">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>$C5="Moq"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="2">
+    <cfRule type="expression" dxfId="26" priority="2">
       <formula>$C5="Database finto"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="3">
+    <cfRule type="expression" dxfId="25" priority="3">
       <formula>$C5="Puro"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="4">
+    <cfRule type="expression" dxfId="24" priority="4">
       <formula>$C5="Puro (senza dipendenze)"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="5">
+    <cfRule type="expression" dxfId="23" priority="5">
       <formula>$C5="Validatore"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="6">
+    <cfRule type="expression" dxfId="22" priority="6">
       <formula>$C5="AutoMapper vero"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="7">
+    <cfRule type="expression" dxfId="21" priority="7">
       <formula>$C5="Database finto + Moq"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7455,7 +8075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E5FAD"/>
@@ -7469,15 +8089,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>925</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
+      <c r="A1" s="30" t="s">
+        <v>923</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>141</v>
@@ -7485,79 +8105,79 @@
     </row>
     <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
+        <v>925</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>926</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>927</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>928</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>928</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>929</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>930</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>931</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -7568,7 +8188,7 @@
         <v>533</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -7576,10 +8196,10 @@
         <v>234</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -7590,7 +8210,7 @@
         <v>640</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -7598,10 +8218,10 @@
         <v>234</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -7609,87 +8229,87 @@
         <v>234</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
+        <v>949</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>950</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>951</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>952</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
+        <v>962</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>963</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>964</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>965</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -7697,7 +8317,7 @@
         <v>337</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>338</v>
@@ -7708,65 +8328,65 @@
         <v>337</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
+        <v>968</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>969</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>970</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>971</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
   </sheetData>
@@ -7774,22 +8394,22 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A1000">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>$A5="JWT"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="2">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>$A5="Ruoli"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>$A5="Account"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="4">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>$A5="Sessione"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="5">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>$A5="Primo avvio"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="6">
+    <cfRule type="expression" dxfId="15" priority="6">
       <formula>$A5="Protezioni"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7803,7 +8423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E5FAD"/>
@@ -7820,18 +8440,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>981</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="A1" s="30" t="s">
+        <v>979</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>141</v>
@@ -7839,22 +8459,22 @@
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
+        <v>981</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>983</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>984</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>985</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>361</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.3">
@@ -7862,19 +8482,19 @@
         <v>695</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>986</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>987</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>988</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>989</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>990</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>693</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -7882,19 +8502,19 @@
         <v>698</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>990</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>991</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>992</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>993</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>994</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>696</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
   </sheetData>
@@ -7911,7 +8531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E5FAD"/>
@@ -7929,19 +8549,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>996</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="A1" s="30" t="s">
+        <v>994</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>141</v>
@@ -7949,22 +8569,22 @@
     </row>
     <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
+        <v>996</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>997</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>998</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>999</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="E4" s="13" t="s">
         <v>1000</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>1001</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>1002</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>1003</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>147</v>
@@ -7975,13 +8595,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C5" s="17">
         <v>45981</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>152</v>
@@ -7996,13 +8616,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C6" s="17">
         <v>46092</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>152</v>
@@ -8011,7 +8631,7 @@
         <v>152</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
@@ -8019,13 +8639,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C7" s="17">
         <v>46259</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>152</v>
@@ -8040,13 +8660,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C8" s="17">
         <v>46260</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>152</v>
@@ -8055,7 +8675,7 @@
         <v>152</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
@@ -8063,13 +8683,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C9" s="17">
         <v>46265</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>152</v>
@@ -8078,7 +8698,7 @@
         <v>152</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
@@ -8086,13 +8706,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C10" s="17">
         <v>46267</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>152</v>
@@ -8101,7 +8721,7 @@
         <v>152</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.3">
@@ -8109,13 +8729,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C11" s="17">
         <v>46269</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>152</v>
@@ -8130,18 +8750,18 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E1000">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>$E5="Sì"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="2">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>$E5="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F1000">
-    <cfRule type="expression" dxfId="23" priority="3">
+    <cfRule type="expression" dxfId="12" priority="3">
       <formula>$F5="Sì"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="4">
+    <cfRule type="expression" dxfId="11" priority="4">
       <formula>$F5="No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8160,7 +8780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
@@ -8175,16 +8795,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>141</v>
@@ -8195,10 +8815,10 @@
         <v>55</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>361</v>
@@ -8206,170 +8826,170 @@
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>1026</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="8" t="s">
         <v>1027</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>1030</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="D6" s="8" t="s">
         <v>1031</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>1034</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="D7" s="8" t="s">
         <v>1035</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>1038</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>562</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>562</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>562</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>562</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>564</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>533</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>1059</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>1062</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>1064</v>
       </c>
     </row>
   </sheetData>
@@ -8377,10 +8997,10 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C1000">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$C5="Tutti"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>$C5="Admin"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8394,7 +9014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
@@ -8409,16 +9029,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>141</v>
@@ -8426,7 +9046,7 @@
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>145</v>
@@ -8435,228 +9055,228 @@
         <v>361</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>1068</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>1070</v>
-      </c>
       <c r="D5" s="8" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>542</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>1086</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>1089</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="D15" s="8" t="s">
         <v>1090</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>1093</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>1095</v>
-      </c>
       <c r="D16" s="8" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>1096</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>1101</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>188</v>
@@ -8664,27 +9284,27 @@
     </row>
     <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>1106</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>188</v>
@@ -8692,142 +9312,142 @@
     </row>
     <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>1115</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>1118</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>1123</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>1126</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="D32" s="8" t="s">
         <v>1134</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>1136</v>
       </c>
     </row>
   </sheetData>
@@ -8835,16 +9455,16 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B1000">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$B5="Finestra"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>$B5="Condiviso"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>$B5="Struttura"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>$B5="UI base"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8858,12 +9478,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -8875,18 +9495,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>1137</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>141</v>
@@ -8894,7 +9514,7 @@
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>252</v>
@@ -8903,7 +9523,7 @@
         <v>517</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>361</v>
@@ -8914,7 +9534,7 @@
     </row>
     <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>149</v>
@@ -8923,18 +9543,18 @@
         <v>531</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>376</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>149</v>
@@ -8943,18 +9563,18 @@
         <v>531</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>149</v>
@@ -8963,18 +9583,18 @@
         <v>522</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>572</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>149</v>
@@ -8983,18 +9603,18 @@
         <v>539</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>575</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>149</v>
@@ -9003,18 +9623,18 @@
         <v>543</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>259</v>
@@ -9023,18 +9643,18 @@
         <v>531</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>393</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>259</v>
@@ -9043,18 +9663,18 @@
         <v>531</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>259</v>
@@ -9063,18 +9683,18 @@
         <v>522</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>594</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>259</v>
@@ -9083,18 +9703,18 @@
         <v>539</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>597</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>259</v>
@@ -9103,18 +9723,18 @@
         <v>543</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>402</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>277</v>
@@ -9123,18 +9743,18 @@
         <v>531</v>
       </c>
       <c r="D15" s="8" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F15" s="14" t="s">
         <v>1167</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>277</v>
@@ -9143,18 +9763,18 @@
         <v>531</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>410</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>277</v>
@@ -9163,18 +9783,18 @@
         <v>531</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>444</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>277</v>
@@ -9183,18 +9803,18 @@
         <v>522</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>615</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>277</v>
@@ -9203,18 +9823,18 @@
         <v>539</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>618</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>277</v>
@@ -9223,18 +9843,18 @@
         <v>543</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>425</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>188</v>
@@ -9243,18 +9863,18 @@
         <v>531</v>
       </c>
       <c r="D21" s="8" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>1181</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>1182</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>188</v>
@@ -9263,18 +9883,18 @@
         <v>522</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>188</v>
@@ -9283,18 +9903,18 @@
         <v>539</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>645</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>188</v>
@@ -9303,18 +9923,18 @@
         <v>576</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>188</v>
@@ -9323,18 +9943,18 @@
         <v>576</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>188</v>
@@ -9343,18 +9963,18 @@
         <v>576</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>188</v>
@@ -9363,18 +9983,18 @@
         <v>543</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>296</v>
@@ -9383,38 +10003,38 @@
         <v>522</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F28" s="14" t="s">
         <v>1202</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
-        <v>1205</v>
+        <v>1361</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>531</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>1206</v>
+        <v>1362</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>660</v>
+        <v>1363</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>309</v>
@@ -9423,261 +10043,261 @@
         <v>531</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>228</v>
+        <v>309</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>531</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>1212</v>
+        <v>663</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>1213</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>228</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>228</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>228</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>228</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>549</v>
+        <v>1220</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>228</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>1227</v>
+        <v>549</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>228</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>1234</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>337</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1033</v>
+        <v>1231</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>1037</v>
+        <v>337</v>
       </c>
       <c r="C40" s="14" t="s">
         <v>522</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>528</v>
+        <v>1031</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>1239</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>522</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>1241</v>
+        <v>528</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
-        <v>1242</v>
+        <v>1235</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>1243</v>
+        <v>1035</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>78</v>
+        <v>1238</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>78</v>
@@ -9686,30 +10306,50 @@
         <v>78</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="F43" s="14" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E44" s="8" t="s">
         <v>1245</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>1243</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:C1000">
-    <cfRule type="expression" dxfId="15" priority="1">
+  <conditionalFormatting sqref="C5:C1001">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$C5="GET"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>$C5="POST"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$C5="PUT"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>$C5="PATCH"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>$C5="DELETE"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9723,7 +10363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
@@ -9737,15 +10377,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>1248</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>141</v>
@@ -9753,35 +10393,35 @@
     </row>
     <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>54</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>1250</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>1253</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -9789,43 +10429,43 @@
         <v>234</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>1257</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>1260</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>1261</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -9833,76 +10473,76 @@
         <v>337</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>1267</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>1270</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>1273</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>1276</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>1281</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>1283</v>
       </c>
     </row>
   </sheetData>
@@ -9919,168 +10559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF2E7D32"/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="64" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>1284</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-    </row>
-    <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
-      <c r="A3" s="15" t="s">
-        <v>879</v>
-      </c>
-      <c r="B3" s="18">
-        <f>SUM(C5:C1000)</f>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>1286</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>881</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C5" s="14">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>1289</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>1290</v>
-      </c>
-      <c r="C6" s="14">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C7" s="14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C8" s="14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>1296</v>
-      </c>
-      <c r="C9" s="14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>1297</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C10" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>1299</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C11" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>1301</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C12" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>1304</v>
-      </c>
-      <c r="C13" s="14">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C2" location="'Dashboard'!A1" display="← Torna alla Dashboard" xr:uid="{00000000-0004-0000-1100-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC55A11"/>
@@ -10096,18 +10575,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
-        <v>1305</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="A1" s="28" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>141</v>
@@ -10115,16 +10594,16 @@
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>252</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>72</v>
@@ -10141,16 +10620,16 @@
         <v>125</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="D5" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>1310</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>1331</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.3">
@@ -10161,16 +10640,16 @@
         <v>359</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>1313</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1314</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>1331</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.3">
@@ -10178,16 +10657,16 @@
         <v>46297</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>1316</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>1317</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>1318</v>
-      </c>
       <c r="E7" s="14" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="F7" s="8"/>
     </row>
@@ -10199,16 +10678,16 @@
         <v>125</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>1319</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>1320</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>1331</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -10218,13 +10697,13 @@
       <c r="B9" s="14"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.3">
@@ -10232,17 +10711,17 @@
         <v>46300</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -13340,16 +13819,16 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E1000">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>$E5="Fatto"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="58" priority="2">
       <formula>$E5="In corso"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="57" priority="3">
       <formula>$E5="Da fare"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="56" priority="4">
       <formula>$E5="Sospeso"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13371,954 +13850,159 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF2E5FAD"/>
+    <tabColor rgb="FF2E7D32"/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="70" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="64" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-    </row>
-    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+    </row>
+    <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F2" s="12" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
+      <c r="A3" s="15" t="s">
+        <v>877</v>
+      </c>
+      <c r="B3" s="18">
+        <f>SUM(C5:C1000)</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>142</v>
+        <v>1284</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>143</v>
+        <v>879</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+        <v>1285</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C5" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+        <v>1287</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C6" s="14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+        <v>1289</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C7" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+        <v>1291</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C8" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+        <v>1293</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C9" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+        <v>1295</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C10" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+        <v>1297</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C11" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+        <v>1299</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C12" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A22" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A28" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A29" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A30" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A34" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A35" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A36" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A38" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A40" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A41" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A42" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A43" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A45" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A46" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A47" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A48" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>248</v>
+        <v>1301</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C13" s="14">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E1000">
-    <cfRule type="expression" dxfId="59" priority="1">
-      <formula>$E5="Sì"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="2">
-      <formula>$E5="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F2" location="'Dashboard'!A1" display="← Torna alla Dashboard" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="C2" location="'Dashboard'!A1" display="← Torna alla Dashboard" xr:uid="{00000000-0004-0000-1100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -14327,7 +14011,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC55A11"/>
@@ -14347,21 +14031,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
-        <v>1322</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
+      <c r="A1" s="28" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
     </row>
     <row r="2" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>141</v>
@@ -14369,10 +14053,10 @@
     </row>
     <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>252</v>
@@ -14381,93 +14065,123 @@
         <v>54</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>74</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>72</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="45" x14ac:dyDescent="0.3">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="B5" s="17">
         <v>46297</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>85</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>1330</v>
+        <v>1345</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="I5" s="17"/>
+        <v>79</v>
+      </c>
+      <c r="I5" s="17">
+        <v>46301</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="B6" s="17">
         <v>46300</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="14" t="s">
         <v>85</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="H6" s="14" t="s">
         <v>84</v>
       </c>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="8"/>
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B7" s="17">
+        <v>46301</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>1343</v>
+      </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="14"/>
+      <c r="F7" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="G7" s="8"/>
-      <c r="H7" s="14"/>
+      <c r="H7" s="14" t="s">
+        <v>88</v>
+      </c>
       <c r="I7" s="17"/>
     </row>
-    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="14"/>
+    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B8" s="17">
+        <v>46301</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>1350</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>84</v>
+      </c>
       <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -18625,27 +18339,27 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F1000">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>$F5="Alta"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="54" priority="2">
       <formula>$F5="Media"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="53" priority="3">
       <formula>$F5="Bassa"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H1000">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="52" priority="4">
       <formula>$H5="Risolto"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="51" priority="5">
       <formula>$H5="In corso"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6">
+    <cfRule type="expression" dxfId="50" priority="6">
       <formula>$H5="Aperto"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="49" priority="7">
       <formula>$H5="Scartato"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18670,12 +18384,968 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF2E5FAD"/>
+  </sheetPr>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+    </row>
+    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A30" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A32" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A33" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A34" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A35" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A36" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A37" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A38" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A39" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A40" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A41" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A42" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A43" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A45" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A46" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A47" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A48" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E5:E1000">
+    <cfRule type="expression" dxfId="48" priority="1">
+      <formula>$E5="Sì"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="47" priority="2">
+      <formula>$E5="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="F2" location="'Dashboard'!A1" display="← Torna alla Dashboard" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E5FAD"/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -18685,12 +19355,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -18954,211 +19624,225 @@
     </row>
     <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>308</v>
+        <v>1354</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>310</v>
+        <v>1355</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>311</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>309</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>309</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>309</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>228</v>
+        <v>309</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>228</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>228</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>228</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>228</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>228</v>
+        <v>337</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>344</v>
+        <v>228</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>344</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>351</v>
       </c>
       <c r="C36" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A37" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D37" s="8" t="s">
         <v>356</v>
       </c>
     </row>
@@ -19176,7 +19860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E5FAD"/>
@@ -19191,12 +19875,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -19677,7 +20361,7 @@
         <v>436</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" x14ac:dyDescent="0.3">
@@ -19770,7 +20454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E5FAD"/>
@@ -19787,14 +20471,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>448</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -20139,16 +20823,16 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B1000">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="46" priority="1">
       <formula>$B5="Servizio"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="2">
+    <cfRule type="expression" dxfId="45" priority="2">
       <formula>$B5="Motore"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="3">
+    <cfRule type="expression" dxfId="44" priority="3">
       <formula>$B5="Supporto"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="4">
+    <cfRule type="expression" dxfId="43" priority="4">
       <formula>$B5="Framework"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20162,12 +20846,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E5FAD"/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -20180,15 +20864,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>513</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -20203,8 +20887,8 @@
         <v>515</v>
       </c>
       <c r="B3" s="16">
-        <f>COUNTA(A5:A1000)</f>
-        <v>54</v>
+        <f>COUNTA(A5:A1001)</f>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -21032,24 +21716,24 @@
       </c>
       <c r="G42" s="14"/>
     </row>
-    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="30" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>191</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>628</v>
+        <v>1351</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>564</v>
+        <v>524</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>629</v>
+        <v>1352</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>630</v>
+        <v>1353</v>
       </c>
       <c r="G43" s="14"/>
     </row>
@@ -21058,19 +21742,19 @@
         <v>191</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>564</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="G44" s="14"/>
     </row>
@@ -21082,16 +21766,16 @@
         <v>531</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="G45" s="14"/>
     </row>
@@ -21103,16 +21787,16 @@
         <v>531</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>562</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>432</v>
+        <v>636</v>
       </c>
       <c r="G46" s="14"/>
     </row>
@@ -21124,16 +21808,16 @@
         <v>531</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>640</v>
+        <v>562</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>642</v>
+        <v>432</v>
       </c>
       <c r="G47" s="14"/>
     </row>
@@ -21142,19 +21826,19 @@
         <v>191</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>564</v>
+        <v>640</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="G48" s="14"/>
     </row>
@@ -21163,19 +21847,19 @@
         <v>191</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>576</v>
+        <v>539</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="G49" s="14"/>
     </row>
@@ -21187,16 +21871,16 @@
         <v>576</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>562</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G50" s="14"/>
     </row>
@@ -21208,16 +21892,16 @@
         <v>576</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="G51" s="14"/>
     </row>
@@ -21226,40 +21910,40 @@
         <v>191</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>543</v>
+        <v>576</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>533</v>
+        <v>564</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="G52" s="14"/>
     </row>
     <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
-        <v>309</v>
+        <v>191</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>562</v>
+        <v>533</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G53" s="14"/>
     </row>
@@ -21271,37 +21955,37 @@
         <v>531</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>562</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G54" s="14"/>
     </row>
     <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
-        <v>664</v>
+        <v>309</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>531</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>533</v>
+        <v>562</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="G55" s="14"/>
     </row>
@@ -21313,87 +21997,108 @@
         <v>531</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D56" s="14" t="s">
         <v>533</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="G56" s="14"/>
     </row>
     <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>533</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="G57" s="14"/>
     </row>
     <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A58" s="14" t="s">
+        <v>671</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>673</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="G58" s="14"/>
+    </row>
+    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A59" s="14" t="s">
         <v>675</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B59" s="14" t="s">
         <v>531</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C59" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D59" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E59" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F58" s="8" t="s">
+      <c r="F59" s="8" t="s">
         <v>677</v>
       </c>
-      <c r="G58" s="14"/>
+      <c r="G59" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:B1000">
-    <cfRule type="expression" dxfId="53" priority="1">
+  <conditionalFormatting sqref="B5:B1001">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>$B5="GET"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="2">
+    <cfRule type="expression" dxfId="41" priority="2">
       <formula>$B5="POST"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="3">
+    <cfRule type="expression" dxfId="40" priority="3">
       <formula>$B5="PUT"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="4">
+    <cfRule type="expression" dxfId="39" priority="4">
       <formula>$B5="PATCH"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="5">
+    <cfRule type="expression" dxfId="38" priority="5">
       <formula>$B5="DELETE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D1000">
-    <cfRule type="expression" dxfId="48" priority="6">
+  <conditionalFormatting sqref="D5:D1001">
+    <cfRule type="expression" dxfId="37" priority="6">
       <formula>$D5="Pubblico"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="7">
+    <cfRule type="expression" dxfId="36" priority="7">
       <formula>$D5="Admin"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21407,7 +22112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E5FAD"/>
@@ -21423,13 +22128,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>678</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="2" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -22566,10 +23271,10 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C1000">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>$C5="Pubblico"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="2">
+    <cfRule type="expression" dxfId="34" priority="2">
       <formula>$C5="Interno"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22581,559 +23286,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF2E5FAD"/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="90" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>787</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-    </row>
-    <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>789</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>790</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>792</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>794</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>796</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
-        <v>798</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
-        <v>800</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>802</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>804</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>806</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>808</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>809</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C2" location="'Dashboard'!A1" display="← Torna alla Dashboard" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF2E5FAD"/>
-  </sheetPr>
-  <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="90" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>810</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-    </row>
-    <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>812</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>813</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>814</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>816</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>817</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>819</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>817</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
-        <v>821</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>817</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
-        <v>823</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>817</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>825</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>817</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>827</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>817</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>784</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>817</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>830</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>817</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>832</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>833</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
-        <v>835</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>833</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
-        <v>837</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>833</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>839</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>833</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>841</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>833</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>843</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
-        <v>846</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
-        <v>848</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A22" s="14" t="s">
-        <v>850</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>852</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>854</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
-        <v>856</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
-        <v>858</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A28" s="14" t="s">
-        <v>862</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>863</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A29" s="14" t="s">
-        <v>865</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>863</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A30" s="14" t="s">
-        <v>867</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>863</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
-        <v>869</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
-        <v>871</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
-        <v>873</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A34" s="14" t="s">
-        <v>875</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>876</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B5:B1000">
-    <cfRule type="expression" dxfId="44" priority="1">
-      <formula>$B5="Middleware"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="2">
-      <formula>$B5="Eccezione"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="3">
-      <formula>$B5="Estensione"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="41" priority="4">
-      <formula>$B5="Configurazione"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="5">
-      <formula>$B5="Riga di comando"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="6">
-      <formula>$B5="Deploy"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C2" location="'Dashboard'!A1" display="← Torna alla Dashboard" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>